--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="53">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>
@@ -266,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -331,6 +331,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
@@ -725,7 +730,7 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="93">
+      <c r="C2" t="s" s="98">
         <v>19</v>
       </c>
     </row>
@@ -736,7 +741,7 @@
       <c r="B3" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="94">
+      <c r="C3" t="s" s="99">
         <v>19</v>
       </c>
     </row>
@@ -747,7 +752,7 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s" s="95">
+      <c r="C4" t="s" s="100">
         <v>19</v>
       </c>
     </row>
@@ -758,7 +763,7 @@
       <c r="B5" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C5" t="s" s="96">
+      <c r="C5" t="s" s="101">
         <v>19</v>
       </c>
     </row>
@@ -769,7 +774,7 @@
       <c r="B6" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="C6" t="s" s="97">
+      <c r="C6" t="s" s="102">
         <v>19</v>
       </c>
     </row>

--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="53">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>
@@ -266,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -365,6 +365,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
@@ -730,8 +736,8 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="98">
-        <v>19</v>
+      <c r="C2" t="s" s="103">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -741,7 +747,7 @@
       <c r="B3" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="99">
+      <c r="C3" t="s" s="104">
         <v>19</v>
       </c>
     </row>
@@ -752,7 +758,7 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s" s="100">
+      <c r="C4" t="s" s="105">
         <v>19</v>
       </c>
     </row>
@@ -763,7 +769,7 @@
       <c r="B5" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C5" t="s" s="101">
+      <c r="C5" t="s" s="106">
         <v>19</v>
       </c>
     </row>
@@ -774,7 +780,7 @@
       <c r="B6" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="C6" t="s" s="102">
+      <c r="C6" t="s" s="107">
         <v>19</v>
       </c>
     </row>
@@ -785,7 +791,7 @@
       <c r="B7" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C7" t="s" s="66">
+      <c r="C7" t="s" s="108">
         <v>19</v>
       </c>
     </row>

--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="53">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>
@@ -266,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -365,6 +365,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
@@ -736,7 +748,7 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="103">
+      <c r="C2" t="s" s="115">
         <v>20</v>
       </c>
     </row>
@@ -747,7 +759,7 @@
       <c r="B3" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="104">
+      <c r="C3" t="s" s="116">
         <v>19</v>
       </c>
     </row>
@@ -758,7 +770,7 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s" s="105">
+      <c r="C4" t="s" s="117">
         <v>19</v>
       </c>
     </row>
@@ -769,7 +781,7 @@
       <c r="B5" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C5" t="s" s="106">
+      <c r="C5" t="s" s="118">
         <v>19</v>
       </c>
     </row>
@@ -780,7 +792,7 @@
       <c r="B6" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="C6" t="s" s="107">
+      <c r="C6" t="s" s="119">
         <v>19</v>
       </c>
     </row>
@@ -791,7 +803,7 @@
       <c r="B7" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C7" t="s" s="108">
+      <c r="C7" t="s" s="120">
         <v>19</v>
       </c>
     </row>

--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohdw\eclipse-workspace\OpencartV121\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79915003-83F8-42F0-9FCB-354A6F3A533A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D512B63-DAA2-4409-A577-6A985E9ABA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{EF90297E-2924-423C-A1BA-B993ED0F546D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{EF90297E-2924-423C-A1BA-B993ED0F546D}"/>
   </bookViews>
   <sheets>
     <sheet name="Register_Data" sheetId="4" r:id="rId1"/>
+    <sheet name="Search" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>
@@ -198,6 +199,24 @@
   </si>
   <si>
     <t>ZBZ326</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>imac</t>
+  </si>
+  <si>
+    <t>macbook pro</t>
+  </si>
+  <si>
+    <t>$122.00</t>
+  </si>
+  <si>
+    <t>$2,000.00</t>
   </si>
 </sst>
 </file>
@@ -234,22 +253,22 @@
       </patternFill>
     </fill>
     <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
       <patternFill patternType="none">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="10"/>
       </patternFill>
     </fill>
@@ -266,128 +285,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,8 +659,8 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="115">
-        <v>20</v>
+      <c r="C2" t="s" s="10">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -759,7 +670,7 @@
       <c r="B3" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="116">
+      <c r="C3" t="s" s="11">
         <v>19</v>
       </c>
     </row>
@@ -770,7 +681,7 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s" s="117">
+      <c r="C4" t="s" s="12">
         <v>19</v>
       </c>
     </row>
@@ -781,7 +692,7 @@
       <c r="B5" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C5" t="s" s="118">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -792,7 +703,7 @@
       <c r="B6" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="C6" t="s" s="119">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -803,7 +714,7 @@
       <c r="B7" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="C7" t="s" s="120">
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -814,165 +725,165 @@
       <c r="B8" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="C8" t="s" s="67">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s" s="0">
         <v>17</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="C9" t="s" s="68">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s" s="0">
         <v>21</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C10" t="s" s="69">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s" s="0">
         <v>23</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C11" t="s" s="70">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s" s="0">
         <v>25</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C12" t="s" s="71">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s" s="0">
         <v>27</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="C13" t="s" s="72">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="C13" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s" s="0">
         <v>29</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="C14" t="s" s="73">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="C14" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s" s="0">
         <v>31</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C15" t="s" s="74">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="C16" t="s" s="75">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s" s="0">
         <v>35</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="C17" t="s" s="76">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="C17" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s" s="0">
         <v>37</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="C18" t="s" s="77">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="C18" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s" s="0">
         <v>39</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="C19" t="s" s="78">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="C19" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s" s="0">
         <v>41</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C20" t="s" s="79">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="C20" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s" s="0">
         <v>43</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C21" t="s" s="80">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="C21" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s" s="0">
         <v>45</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="C22" t="s" s="81">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s" s="0">
         <v>47</v>
       </c>
@@ -980,7 +891,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s" s="0">
         <v>49</v>
       </c>
@@ -988,12 +899,50 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s" s="0">
         <v>51</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD05086-7EB0-4253-BC09-1122616AD83D}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="21.85546875"/>
+    <col min="2" max="2" customWidth="true" width="23.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="60">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>$2,000.00</t>
+  </si>
+  <si>
+    <t>$100.00</t>
   </si>
 </sst>
 </file>
@@ -934,7 +937,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">

--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>

--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="62">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <t>$100.00</t>
+  </si>
+  <si>
+    <t>brsoE@gmail.com</t>
+  </si>
+  <si>
+    <t>eKQ438</t>
   </si>
 </sst>
 </file>
@@ -288,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -300,6 +306,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
@@ -636,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F037367A-B41F-4584-A70E-03EF78EAE709}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="35.42578125"/>
@@ -662,8 +671,8 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="10">
-        <v>19</v>
+      <c r="C2" t="s" s="13">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -673,7 +682,7 @@
       <c r="B3" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="11">
+      <c r="C3" t="s" s="14">
         <v>19</v>
       </c>
     </row>
@@ -684,7 +693,7 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s" s="12">
+      <c r="C4" t="s" s="15">
         <v>19</v>
       </c>
     </row>
@@ -908,6 +917,14 @@
       </c>
       <c r="B25" t="s" s="0">
         <v>52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Login_Data.xlsx
+++ b/testdata/Login_Data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="64">
   <si>
     <t>nLNnG@gmail.com</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>eKQ438</t>
+  </si>
+  <si>
+    <t>LSnxl@gmail.com</t>
+  </si>
+  <si>
+    <t>ZLa317</t>
   </si>
 </sst>
 </file>
@@ -294,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -309,6 +315,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
@@ -645,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F037367A-B41F-4584-A70E-03EF78EAE709}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="35.42578125"/>
@@ -671,8 +683,8 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="13">
-        <v>20</v>
+      <c r="C2" t="s" s="20">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -682,7 +694,7 @@
       <c r="B3" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="C3" t="s" s="14">
+      <c r="C3" t="s" s="21">
         <v>19</v>
       </c>
     </row>
@@ -925,6 +937,14 @@
       </c>
       <c r="B26" t="s" s="0">
         <v>61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
